--- a/cet4/result/61_职场女王_逆风翱翔的逆袭路/61_职场女王_逆风翱翔的逆袭路_学习版.xlsx
+++ b/cet4/result/61_职场女王_逆风翱翔的逆袭路/61_职场女王_逆风翱翔的逆袭路_学习版.xlsx
@@ -397,745 +397,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D49"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>president</v>
       </c>
       <c r="B2" t="str">
-        <v>president</v>
+        <v>/ˈprezɪdənt/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>总裁</v>
       </c>
-      <c r="D2" t="str">
-        <v>president(总裁)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>chief</v>
       </c>
       <c r="B3" t="str">
-        <v>chief</v>
+        <v>/tʃiːf/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D3" t="str">
         <v>首席</v>
       </c>
-      <c r="D3" t="str">
-        <v>chief(首席)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>mechanically</v>
       </c>
       <c r="B4" t="str">
-        <v>mechanically</v>
+        <v>/məˈkænɪkli/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D4" t="str">
         <v>机械地</v>
       </c>
-      <c r="D4" t="str">
-        <v>mechanically(机械地)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>outset</v>
       </c>
       <c r="B5" t="str">
-        <v>outset</v>
+        <v>/ˈaʊtset/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>开始</v>
       </c>
-      <c r="D5" t="str">
-        <v>outset(开始)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>aim</v>
       </c>
       <c r="B6" t="str">
-        <v>aim</v>
+        <v>/eɪm/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D6" t="str">
         <v>目标</v>
       </c>
-      <c r="D6" t="str">
-        <v>aim(目标)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>slippery</v>
       </c>
       <c r="B7" t="str">
-        <v>slippery</v>
+        <v>/ˈslɪpəri/</v>
       </c>
       <c r="C7" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>滑的；狡猾的</v>
       </c>
-      <c r="D7" t="str">
-        <v>slippery(滑的；狡猾的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>hi</v>
       </c>
       <c r="B8" t="str">
-        <v>hi</v>
+        <v>/haɪ/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./int.</v>
+      </c>
+      <c r="D8" t="str">
         <v>嗨！</v>
       </c>
-      <c r="D8" t="str">
-        <v>hi(嗨！)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>room</v>
       </c>
       <c r="B9" t="str">
-        <v>room</v>
+        <v>/ruːm,rʊm/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>房间</v>
       </c>
-      <c r="D9" t="str">
-        <v>room(房间)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>classical</v>
       </c>
       <c r="B10" t="str">
-        <v>classical</v>
+        <v>/ˈklæsɪkl/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>古典的</v>
       </c>
-      <c r="D10" t="str">
-        <v>classical(古典的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>unstable</v>
       </c>
       <c r="B11" t="str">
-        <v>unstable</v>
+        <v>/ʌnˈsteɪbl/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>不稳定的</v>
       </c>
-      <c r="D11" t="str">
-        <v>unstable(不稳定的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>we</v>
       </c>
       <c r="B12" t="str">
-        <v>we</v>
+        <v>/wi,wiː/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D12" t="str">
         <v>我们</v>
       </c>
-      <c r="D12" t="str">
-        <v>we(我们)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>increasingly</v>
       </c>
       <c r="B13" t="str">
-        <v>increasingly</v>
+        <v>/ɪnˈkriːsɪŋli/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D13" t="str">
         <v>越来越多地</v>
       </c>
-      <c r="D13" t="str">
-        <v>increasingly(越来越多地)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>definitely</v>
       </c>
       <c r="B14" t="str">
-        <v>definitely</v>
+        <v>/ˈdefɪnətli/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D14" t="str">
         <v>清楚地，当然</v>
       </c>
-      <c r="D14" t="str">
-        <v>definitely(清楚地，当然)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>engine</v>
       </c>
       <c r="B15" t="str">
-        <v>engine</v>
+        <v>/ˈendʒɪn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>引擎</v>
       </c>
-      <c r="D15" t="str">
-        <v>engine(引擎)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>probably</v>
       </c>
       <c r="B16" t="str">
-        <v>probably</v>
+        <v>/ˈprɑːbəbli/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D16" t="str">
         <v>大概</v>
       </c>
-      <c r="D16" t="str">
-        <v>probably(大概)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>can</v>
       </c>
       <c r="B17" t="str">
-        <v>can</v>
+        <v>/kæn; kən/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./conj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>能</v>
       </c>
-      <c r="D17" t="str">
-        <v>can(能)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>classification</v>
       </c>
       <c r="B18" t="str">
-        <v>classification</v>
+        <v>/ˌklæsɪfɪˈkeɪʃn/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>分类</v>
       </c>
-      <c r="D18" t="str">
-        <v>classification(分类)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>blend</v>
       </c>
       <c r="B19" t="str">
-        <v>blend</v>
+        <v>/blend/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>混合</v>
       </c>
-      <c r="D19" t="str">
-        <v>blend(混合)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>pollute</v>
       </c>
       <c r="B20" t="str">
-        <v>pollute</v>
+        <v>/pəˈluːt/</v>
       </c>
       <c r="C20" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D20" t="str">
         <v>污染</v>
       </c>
-      <c r="D20" t="str">
-        <v>pollute(污染)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>assembly</v>
       </c>
       <c r="B21" t="str">
-        <v>assembly</v>
+        <v>/əˈsembli/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>装配</v>
       </c>
-      <c r="D21" t="str">
-        <v>assembly(装配)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>operate</v>
       </c>
       <c r="B22" t="str">
-        <v>operate</v>
+        <v>/ˈɑːpəreɪt/</v>
       </c>
       <c r="C22" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>操作</v>
       </c>
-      <c r="D22" t="str">
-        <v>operate(操作)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>singular</v>
       </c>
       <c r="B23" t="str">
-        <v>singular</v>
+        <v>/ˈsɪŋɡjələr/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>非凡的</v>
       </c>
-      <c r="D23" t="str">
-        <v>singular(非凡的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>accomplish</v>
       </c>
       <c r="B24" t="str">
-        <v>accomplish</v>
+        <v>/əˈkɑːmplɪʃ/</v>
       </c>
       <c r="C24" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D24" t="str">
         <v>完成</v>
       </c>
-      <c r="D24" t="str">
-        <v>accomplish(完成)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>impressive</v>
       </c>
       <c r="B25" t="str">
-        <v>impressive</v>
+        <v>/ɪmˈpresɪv/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>感人的</v>
       </c>
-      <c r="D25" t="str">
-        <v>impressive(感人的)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>price</v>
       </c>
       <c r="B26" t="str">
-        <v>price</v>
+        <v>/praɪs/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D26" t="str">
         <v>价格</v>
       </c>
-      <c r="D26" t="str">
-        <v>price(价格)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>quarrel</v>
       </c>
       <c r="B27" t="str">
-        <v>quarrel</v>
+        <v>/ˈkwɑːrəl/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D27" t="str">
         <v>吵架</v>
       </c>
-      <c r="D27" t="str">
-        <v>quarrel(吵架)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>valuable</v>
       </c>
       <c r="B28" t="str">
-        <v>valuable</v>
+        <v>/ˈvæljuəbl/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>有价值的</v>
       </c>
-      <c r="D28" t="str">
-        <v>valuable(有价值的)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>delete</v>
       </c>
       <c r="B29" t="str">
-        <v>delete</v>
+        <v>/dɪˈliːt/</v>
       </c>
       <c r="C29" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D29" t="str">
         <v>删除</v>
       </c>
-      <c r="D29" t="str">
-        <v>delete(删除)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>nonsense</v>
       </c>
       <c r="B30" t="str">
-        <v>nonsense</v>
+        <v>/ˈnɑːnsens,ˈnɑːnsns/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./adj./int.</v>
+      </c>
+      <c r="D30" t="str">
         <v>胡说</v>
       </c>
-      <c r="D30" t="str">
-        <v>nonsense(胡说)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>injury</v>
       </c>
       <c r="B31" t="str">
-        <v>injury</v>
+        <v>/ˈɪndʒəri/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>伤害</v>
       </c>
-      <c r="D31" t="str">
-        <v>injury(伤害)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>queue</v>
       </c>
       <c r="B32" t="str">
-        <v>queue</v>
+        <v>/kjuː/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D32" t="str">
         <v>排队</v>
       </c>
-      <c r="D32" t="str">
-        <v>queue(排队)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>faulty</v>
       </c>
       <c r="B33" t="str">
-        <v>faulty</v>
+        <v>/ˈfɔːlti/</v>
       </c>
       <c r="C33" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>有错误的</v>
       </c>
-      <c r="D33" t="str">
-        <v>faulty(有错误的)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>by</v>
       </c>
       <c r="B34" t="str">
-        <v>by</v>
+        <v>/baɪ/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./v./adj./adv./prep.</v>
+      </c>
+      <c r="D34" t="str">
         <v>通过</v>
       </c>
-      <c r="D34" t="str">
-        <v>by(通过)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>fur</v>
       </c>
       <c r="B35" t="str">
-        <v>accomplish</v>
+        <v>/fɜːr/</v>
       </c>
       <c r="C35" t="str">
-        <v>完成</v>
+        <v>n./vt.</v>
       </c>
       <c r="D35" t="str">
-        <v>accomplish(完成)📢</v>
+        <v>皮毛</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>grieve</v>
       </c>
       <c r="B36" t="str">
-        <v>fur</v>
+        <v>/ɡriːv/</v>
       </c>
       <c r="C36" t="str">
-        <v>皮毛</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>fur(皮毛)📢</v>
+        <v>悲伤</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>spin</v>
       </c>
       <c r="B37" t="str">
-        <v>grieve</v>
+        <v>/spɪn/</v>
       </c>
       <c r="C37" t="str">
-        <v>悲伤</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D37" t="str">
-        <v>grieve(悲伤)📢</v>
+        <v>旋转</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>its</v>
       </c>
       <c r="B38" t="str">
-        <v>spin</v>
+        <v>/ɪts/</v>
       </c>
       <c r="C38" t="str">
-        <v>旋转</v>
+        <v>n./pron.</v>
       </c>
       <c r="D38" t="str">
-        <v>spin(旋转)📢</v>
+        <v>它的</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>visual</v>
       </c>
       <c r="B39" t="str">
-        <v>its</v>
+        <v>/ˈvɪʒuəl/</v>
       </c>
       <c r="C39" t="str">
-        <v>它的</v>
+        <v>adj.</v>
       </c>
       <c r="D39" t="str">
-        <v>its(它的)📢</v>
+        <v>视觉的</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>option</v>
       </c>
       <c r="B40" t="str">
-        <v>faulty</v>
+        <v>/ˈɑːpʃn/</v>
       </c>
       <c r="C40" t="str">
-        <v>有错误的</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>faulty(有错误的)📢</v>
+        <v>选项</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>like</v>
       </c>
       <c r="B41" t="str">
-        <v>visual</v>
+        <v>/laɪk/</v>
       </c>
       <c r="C41" t="str">
-        <v>视觉的</v>
+        <v>n./vt./vi./v./adj./adv./prep.</v>
       </c>
       <c r="D41" t="str">
-        <v>visual(视觉的)📢</v>
+        <v>喜欢</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>protective</v>
       </c>
       <c r="B42" t="str">
-        <v>option</v>
+        <v>/prəˈtektɪv/</v>
       </c>
       <c r="C42" t="str">
-        <v>选项</v>
+        <v>adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>option(选项)📢</v>
+        <v>防护的</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>value</v>
       </c>
       <c r="B43" t="str">
-        <v>like</v>
+        <v>/ˈvæljuː/</v>
       </c>
       <c r="C43" t="str">
-        <v>喜欢</v>
+        <v>n./vt.</v>
       </c>
       <c r="D43" t="str">
-        <v>like(喜欢)📢</v>
+        <v>价值</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>upwards</v>
       </c>
       <c r="B44" t="str">
-        <v>protective</v>
+        <v>/ˈʌpwərdz/</v>
       </c>
       <c r="C44" t="str">
-        <v>防护的</v>
+        <v>v./adv.</v>
       </c>
       <c r="D44" t="str">
-        <v>protective(防护的)📢</v>
+        <v>向上</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>anticipate</v>
       </c>
       <c r="B45" t="str">
-        <v>value</v>
+        <v>/ænˈtɪsɪpeɪt/</v>
       </c>
       <c r="C45" t="str">
-        <v>价值</v>
+        <v>v.</v>
       </c>
       <c r="D45" t="str">
-        <v>value(价值)📢</v>
+        <v>预期</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>grasp</v>
       </c>
       <c r="B46" t="str">
-        <v>upwards</v>
+        <v>/ɡræsp/</v>
       </c>
       <c r="C46" t="str">
-        <v>向上</v>
+        <v>n./v.</v>
       </c>
       <c r="D46" t="str">
-        <v>upwards(向上)📢</v>
+        <v>抓住</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>luggage</v>
       </c>
       <c r="B47" t="str">
-        <v>anticipate</v>
+        <v>/ˈlʌɡɪdʒ/</v>
       </c>
       <c r="C47" t="str">
-        <v>预期</v>
+        <v>n.</v>
       </c>
       <c r="D47" t="str">
-        <v>anticipate(预期)📢</v>
+        <v>行李</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>lace</v>
       </c>
       <c r="B48" t="str">
-        <v>grasp</v>
+        <v>/leɪs/</v>
       </c>
       <c r="C48" t="str">
-        <v>抓住</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>grasp(抓住)📢</v>
+        <v>花边</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>tortoise</v>
       </c>
       <c r="B49" t="str">
-        <v>luggage</v>
+        <v>/ˈtɔːrtəs/</v>
       </c>
       <c r="C49" t="str">
-        <v>行李</v>
+        <v>n.</v>
       </c>
       <c r="D49" t="str">
-        <v>luggage(行李)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>lace</v>
-      </c>
-      <c r="C50" t="str">
-        <v>花边</v>
-      </c>
-      <c r="D50" t="str">
-        <v>lace(花边)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>tortoise</v>
-      </c>
-      <c r="C51" t="str">
         <v>乌龟</v>
-      </c>
-      <c r="D51" t="str">
-        <v>tortoise(乌龟)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>classification</v>
-      </c>
-      <c r="C52" t="str">
-        <v>分类</v>
-      </c>
-      <c r="D52" t="str">
-        <v>classification(分类)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
   </ignoredErrors>
 </worksheet>
 </file>